--- a/nr-add-cip/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:39+00:00</t>
+    <t>2026-02-02T15:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-cip/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/nr-add-cip/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="807">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:16+00:00</t>
+    <t>2026-02-23T08:39:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -906,17 +906,11 @@
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
   </si>
   <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/eprescription/ValueSet/fr-medication-code</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
 </t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -950,15 +944,6 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/eprescription/ValueSet/fr-medication-code</t>
-  </si>
-  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
@@ -2028,6 +2013,9 @@
   </si>
   <si>
     <t>The amount of therapeutic or other substance given at one administration event.</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]</t>
@@ -2845,12 +2833,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO129"/>
+  <dimension ref="A1:AO128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="56.53515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="13.8125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6225,26 +6213,24 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y29" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>280</v>
@@ -6262,30 +6248,30 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -6307,7 +6293,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>282</v>
@@ -6381,37 +6367,35 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -6426,16 +6410,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6461,11 +6445,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6483,7 +6469,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -6498,27 +6484,27 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6526,7 +6512,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
@@ -6538,19 +6524,19 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6600,10 +6586,10 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>91</v>
@@ -6615,27 +6601,27 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>232</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6646,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6658,17 +6644,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6717,13 +6701,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -6732,27 +6716,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6760,10 +6744,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6772,16 +6756,16 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6832,13 +6816,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6847,27 +6831,27 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6890,13 +6874,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6947,7 +6931,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6962,27 +6946,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6990,7 +6974,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -7002,16 +6986,16 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7062,7 +7046,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7077,16 +7061,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -7094,10 +7078,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7117,18 +7101,20 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>175</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -7153,13 +7139,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -7177,7 +7163,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7192,16 +7178,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -7209,10 +7195,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7232,20 +7218,18 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7270,13 +7254,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -7294,7 +7278,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7309,7 +7293,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
@@ -7318,7 +7302,7 @@
         <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7326,10 +7310,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7340,7 +7324,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -7352,7 +7336,7 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>356</v>
+        <v>175</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>357</v>
@@ -7360,7 +7344,9 @@
       <c r="M39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7385,13 +7371,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7409,13 +7395,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -7424,27 +7410,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7467,16 +7453,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>175</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7502,13 +7488,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7526,7 +7512,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7541,27 +7527,27 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>368</v>
+        <v>232</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7581,20 +7567,18 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7643,7 +7627,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7658,16 +7642,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7675,10 +7659,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7701,7 +7685,7 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>380</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>381</v>
@@ -7758,7 +7742,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7773,13 +7757,13 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7790,10 +7774,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7816,13 +7800,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7873,7 +7857,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7888,13 +7872,13 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -7905,10 +7889,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7919,7 +7903,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7931,7 +7915,7 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>389</v>
+        <v>215</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>390</v>
@@ -7940,7 +7924,9 @@
         <v>391</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7988,13 +7974,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
@@ -8003,13 +7989,13 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -8020,10 +8006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8043,21 +8029,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
         <v>397</v>
       </c>
+      <c r="N45" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -8081,13 +8067,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -8105,7 +8091,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8120,13 +8106,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8151,7 +8137,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -8163,17 +8149,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>175</v>
+        <v>403</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8198,13 +8182,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -8222,13 +8206,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -8237,13 +8221,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -8254,10 +8238,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8280,13 +8264,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8337,7 +8321,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8352,13 +8336,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -8369,10 +8353,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8380,7 +8364,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>81</v>
@@ -8395,15 +8379,17 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8452,7 +8438,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8467,13 +8453,13 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -8484,10 +8470,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8495,10 +8481,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8510,17 +8496,15 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>421</v>
+        <v>156</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>157</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8569,28 +8553,28 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>159</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>160</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8601,21 +8585,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8627,15 +8611,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8672,31 +8658,31 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8716,14 +8702,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8736,24 +8722,26 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8789,19 +8777,19 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8822,7 +8810,7 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -8840,26 +8828,26 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>430</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>431</v>
@@ -8867,11 +8855,9 @@
       <c r="M52" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>189</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>212</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8920,19 +8906,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8941,21 +8927,21 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>134</v>
+        <v>435</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8978,17 +8964,17 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>435</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9037,7 +9023,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9058,21 +9044,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9083,7 +9069,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -9095,17 +9081,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9130,13 +9118,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -9154,13 +9142,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -9175,21 +9163,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9200,7 +9188,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9212,20 +9200,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9249,13 +9233,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -9279,7 +9263,7 @@
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9294,21 +9278,21 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9319,7 +9303,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9331,7 +9315,7 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>156</v>
+        <v>457</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>458</v>
@@ -9339,8 +9323,12 @@
       <c r="M56" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9388,7 +9376,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9409,21 +9397,21 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9443,23 +9431,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>462</v>
+        <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>157</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9507,7 +9491,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>159</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9519,7 +9503,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9528,7 +9512,7 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>468</v>
+        <v>160</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9539,21 +9523,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9565,15 +9549,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9610,31 +9596,31 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9654,14 +9640,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9674,24 +9660,26 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9727,19 +9715,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9760,7 +9748,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9771,14 +9759,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9791,25 +9779,23 @@
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>212</v>
+        <v>470</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9858,7 +9844,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9870,7 +9856,7 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9879,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>134</v>
+        <v>472</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9890,10 +9876,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9904,7 +9890,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9916,17 +9902,17 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>326</v>
+        <v>474</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9975,19 +9961,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>479</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9996,7 +9982,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -10007,10 +9993,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10030,21 +10016,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>479</v>
+        <v>156</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>480</v>
+        <v>157</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>481</v>
+        <v>158</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>482</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10092,7 +10076,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>483</v>
+        <v>159</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10104,7 +10088,7 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -10113,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>485</v>
+        <v>160</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -10124,21 +10108,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10150,15 +10134,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10195,31 +10181,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10239,21 +10225,23 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D64" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10265,17 +10253,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>136</v>
+        <v>485</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>187</v>
+        <v>486</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10312,16 +10298,16 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>164</v>
@@ -10345,7 +10331,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -10359,11 +10345,9 @@
         <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10381,16 +10365,16 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10441,19 +10425,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>164</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10462,7 +10446,7 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10473,10 +10457,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10499,16 +10483,20 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10556,7 +10544,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10577,7 +10565,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10588,10 +10576,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10614,20 +10602,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O67" t="s" s="2">
         <v>504</v>
       </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10696,7 +10680,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10707,10 +10691,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10733,7 +10717,7 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>508</v>
@@ -10741,8 +10725,12 @@
       <c r="M68" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="N68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10790,7 +10778,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10811,7 +10799,7 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10822,10 +10810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10848,19 +10836,19 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10930,7 +10918,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10941,10 +10929,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10967,20 +10955,16 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>512</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>516</v>
-      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11004,13 +10988,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11028,7 +11012,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11049,7 +11033,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -11060,10 +11044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11086,20 +11070,22 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>111</v>
+        <v>495</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q71" s="2"/>
+      <c r="Q71" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="R71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11119,13 +11105,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11143,7 +11129,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11164,7 +11150,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -11201,7 +11187,7 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>531</v>
@@ -11214,53 +11200,51 @@
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q72" t="s" s="2">
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="R72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11281,7 +11265,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -11292,10 +11276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11318,13 +11302,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11375,7 +11359,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11396,7 +11380,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11407,10 +11391,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11433,13 +11417,13 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11490,7 +11474,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11511,7 +11495,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11522,10 +11506,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11548,13 +11532,13 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>512</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11581,13 +11565,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11605,7 +11589,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11626,7 +11610,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11637,10 +11621,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11651,7 +11635,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11666,12 +11650,14 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11698,11 +11684,9 @@
       <c r="X76" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Y76" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11720,13 +11704,13 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -11741,7 +11725,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>529</v>
+        <v>160</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11752,10 +11736,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11778,16 +11762,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>111</v>
+        <v>551</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11813,11 +11797,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11835,7 +11821,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11867,10 +11853,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11893,7 +11879,7 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>556</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>557</v>
@@ -11904,7 +11890,9 @@
       <c r="N78" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11928,13 +11916,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11952,7 +11940,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11973,7 +11961,7 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>160</v>
+        <v>564</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11984,10 +11972,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11998,7 +11986,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -12010,20 +11998,16 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>566</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -12047,13 +12031,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12071,13 +12055,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -12092,7 +12076,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -12103,10 +12087,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12129,7 +12113,7 @@
         <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>571</v>
+        <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>572</v>
@@ -12137,7 +12121,9 @@
       <c r="M80" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12162,13 +12148,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12186,7 +12172,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12207,7 +12193,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -12218,10 +12204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12244,16 +12230,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>175</v>
+        <v>580</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12279,13 +12265,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12303,7 +12289,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12324,21 +12310,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12361,18 +12347,20 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>585</v>
+        <v>175</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12399,10 +12387,10 @@
         <v>239</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12420,7 +12408,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12441,21 +12429,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12481,16 +12469,14 @@
         <v>175</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12515,13 +12501,11 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12539,7 +12523,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12560,21 +12544,21 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12600,14 +12584,16 @@
         <v>175</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>610</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12636,7 +12622,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12654,7 +12640,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12675,21 +12661,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12700,7 +12686,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12712,20 +12698,16 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>175</v>
+        <v>474</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12749,11 +12731,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12771,13 +12755,13 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
@@ -12792,7 +12776,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12817,7 +12801,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12826,16 +12810,16 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>479</v>
+        <v>156</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>622</v>
+        <v>157</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>623</v>
+        <v>158</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12886,19 +12870,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>624</v>
+        <v>159</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12907,32 +12891,32 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12944,15 +12928,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12989,31 +12975,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13033,21 +13019,23 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="D88" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13059,17 +13047,15 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>136</v>
+        <v>625</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>187</v>
+        <v>626</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13106,16 +13092,16 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>164</v>
@@ -13139,7 +13125,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -13153,11 +13139,9 @@
         <v>628</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13175,19 +13159,21 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13211,13 +13197,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13235,19 +13221,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>164</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13262,15 +13248,15 @@
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13293,17 +13279,19 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>175</v>
+        <v>637</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13328,31 +13316,29 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13373,23 +13359,25 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13410,19 +13398,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13459,17 +13447,19 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AC91" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13490,24 +13480,24 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>82</v>
@@ -13529,19 +13519,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13590,7 +13580,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13611,25 +13601,23 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13650,19 +13638,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L93" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>644</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13699,19 +13687,17 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13732,23 +13718,25 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>648</v>
+        <v>659</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13769,19 +13757,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13818,17 +13806,19 @@
         <v>82</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13849,13 +13839,13 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="95">
@@ -13863,7 +13853,7 @@
         <v>664</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>665</v>
@@ -13888,19 +13878,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13949,7 +13939,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13970,24 +13960,24 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -14009,19 +13999,19 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14070,7 +14060,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14091,25 +14081,23 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14130,19 +14118,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14191,7 +14179,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14212,21 +14200,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14246,23 +14234,19 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>673</v>
+        <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>674</v>
+        <v>157</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>677</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14310,7 +14294,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>678</v>
+        <v>159</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14322,7 +14306,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14331,32 +14315,32 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>679</v>
+        <v>160</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>680</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14368,15 +14352,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14413,31 +14399,31 @@
         <v>82</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14457,21 +14443,21 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14480,20 +14466,18 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>136</v>
+        <v>650</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>187</v>
+        <v>680</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>681</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14530,31 +14514,31 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>164</v>
+        <v>682</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14563,7 +14547,7 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>160</v>
+        <v>683</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14574,10 +14558,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14600,13 +14584,13 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14657,7 +14641,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14678,7 +14662,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14689,10 +14673,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14715,16 +14699,20 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>693</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14772,7 +14760,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14793,7 +14781,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
@@ -14804,10 +14792,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14830,19 +14818,17 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>696</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14891,7 +14877,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14912,7 +14898,7 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14923,10 +14909,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14946,21 +14932,19 @@
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>654</v>
+        <v>702</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>703</v>
-      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -15008,7 +14992,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15026,10 +15010,10 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>705</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -15040,10 +15024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15066,13 +15050,13 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>706</v>
+        <v>156</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>707</v>
+        <v>157</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>708</v>
+        <v>158</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15123,7 +15107,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>705</v>
+        <v>159</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15135,16 +15119,16 @@
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>709</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>710</v>
+        <v>160</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
@@ -15155,21 +15139,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15181,15 +15165,17 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15238,19 +15224,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15270,14 +15256,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15290,24 +15276,26 @@
         <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15355,7 +15343,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15376,7 +15364,7 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
@@ -15387,46 +15375,44 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>136</v>
+        <v>702</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>431</v>
+        <v>711</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>432</v>
+        <v>712</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15474,19 +15460,19 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>433</v>
+        <v>710</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15495,7 +15481,7 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>134</v>
+        <v>714</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
@@ -15506,10 +15492,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15532,17 +15518,15 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>706</v>
+        <v>156</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>715</v>
+        <v>157</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15591,7 +15575,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>714</v>
+        <v>159</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15603,7 +15587,7 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15612,7 +15596,7 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>718</v>
+        <v>160</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15623,21 +15607,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15649,15 +15633,17 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15706,19 +15692,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15738,14 +15724,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15758,24 +15744,26 @@
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15823,7 +15811,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15844,7 +15832,7 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
@@ -15855,46 +15843,42 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>136</v>
+        <v>719</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>431</v>
+        <v>720</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15942,19 +15926,19 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>433</v>
+        <v>718</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -15963,7 +15947,7 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>134</v>
+        <v>722</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
@@ -15974,10 +15958,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16000,13 +15984,13 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16057,7 +16041,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16078,7 +16062,7 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>82</v>
@@ -16089,10 +16073,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16115,7 +16099,7 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>729</v>
@@ -16172,7 +16156,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16193,7 +16177,7 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
@@ -16204,10 +16188,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16230,7 +16214,7 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>733</v>
@@ -16238,8 +16222,12 @@
       <c r="M115" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+      <c r="N115" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16287,7 +16275,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16305,10 +16293,10 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>737</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
@@ -16319,10 +16307,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16345,20 +16333,18 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>736</v>
+        <v>566</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>740</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16406,7 +16392,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16424,24 +16410,24 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16464,17 +16450,15 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>571</v>
+        <v>719</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>746</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16523,7 +16507,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16541,24 +16525,24 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16581,15 +16565,17 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16638,7 +16624,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16656,24 +16642,24 @@
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>755</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16696,17 +16682,15 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>728</v>
+        <v>759</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>759</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16755,7 +16739,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16773,13 +16757,13 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>760</v>
+        <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16787,10 +16771,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16813,7 +16797,7 @@
         <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>763</v>
+        <v>702</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>764</v>
@@ -16870,7 +16854,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16888,13 +16872,13 @@
         <v>82</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>82</v>
+        <v>766</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16902,10 +16886,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16928,13 +16912,13 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>706</v>
+        <v>156</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>768</v>
+        <v>157</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>769</v>
+        <v>158</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16985,7 +16969,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>767</v>
+        <v>159</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16997,16 +16981,16 @@
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>770</v>
+        <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>771</v>
+        <v>160</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17017,21 +17001,21 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17043,15 +17027,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17100,19 +17086,19 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17132,14 +17118,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17152,24 +17138,26 @@
         <v>82</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -17217,7 +17205,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17238,7 +17226,7 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>82</v>
@@ -17249,46 +17237,44 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>136</v>
+        <v>580</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>431</v>
+        <v>772</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>432</v>
+        <v>773</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17312,13 +17298,13 @@
         <v>82</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>82</v>
+        <v>775</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>82</v>
+        <v>776</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>82</v>
@@ -17336,42 +17322,42 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>433</v>
+        <v>771</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>82</v>
+        <v>766</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>134</v>
+        <v>777</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>82</v>
+        <v>778</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17379,7 +17365,7 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>91</v>
@@ -17394,17 +17380,15 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>585</v>
+        <v>175</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>778</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17432,31 +17416,31 @@
         <v>239</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="Z125" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>775</v>
-      </c>
       <c r="AG125" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>91</v>
@@ -17471,24 +17455,24 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17511,13 +17495,13 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>175</v>
+        <v>788</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17544,31 +17528,31 @@
         <v>82</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>786</v>
+        <v>82</v>
       </c>
       <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17583,38 +17567,38 @@
         <v>103</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>82</v>
+        <v>791</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>790</v>
+        <v>82</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>82</v>
+        <v>794</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
@@ -17626,15 +17610,17 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>797</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>798</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17683,13 +17669,13 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>82</v>
@@ -17698,13 +17684,13 @@
         <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>795</v>
+        <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>788</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17715,14 +17701,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>798</v>
+        <v>82</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17741,16 +17727,16 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17800,7 +17786,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17815,135 +17801,18 @@
         <v>103</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>82</v>
+        <v>805</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO129" t="s" s="2">
         <v>82</v>
       </c>
     </row>
